--- a/S001 - Options, Futures, and Other Derivates/Chapter_3 - Hedging Strategies Using Futures/Exercise_3_4.xlsx
+++ b/S001 - Options, Futures, and Other Derivates/Chapter_3 - Hedging Strategies Using Futures/Exercise_3_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/66adef9dbd1ee1e5/Desktop/Main_Development_Folder/Quant_Projects/S001 - Options^J Futures^J and Other Derivates/Chapter_3 - Hedging Strategies Using Futures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3FBF24E-41BA-45BF-B152-B36AD71FE6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{F3FBF24E-41BA-45BF-B152-B36AD71FE6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{448038DD-77DD-4F6A-BB05-F52D62DADC49}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{62595A13-C263-4358-A91E-97D466ABBC1D}"/>
   </bookViews>
